--- a/r5-ELGA-MOPED-335-336-Workflowstatus-Voraussetzungen-aktualisieren/ValueSet-moped-aufnahmeart-valueset.xlsx
+++ b/r5-ELGA-MOPED-335-336-Workflowstatus-Voraussetzungen-aktualisieren/ValueSet-moped-aufnahmeart-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Aufnahmeart</t>
+    <t>AufnahmeartVS</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T10:09:42+00:00</t>
+    <t>2025-02-11T14:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet für die Aufnahmeart des Patienten</t>
+    <t>ValueSet für die Aufnahmeart des Patienten (LKF + Ka-Org)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,22 +99,142 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>geplante stationäre Aufnahme/geplanter ambulanter Besuch (mit vorhergehender Terminvereinbarung, Richtwert: mindestens 24 Stunden)</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>akute stationäre Aufnahme/akuter ambulanter Besuch (ohne vorhergehende Terminvereinbarung)</t>
+    <t>Aufnahme in den allgemein stationären Bereich inkl. Aufnahme auf Intensiveinheiten</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Transfer von einem anderen Krankenhaus in den allgemein stationären Bereich inkl. Intensiveinheiten</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Wiederaufnahme in den allgemein stationären Bereich inkl. Wiederaufnahme auf Intensiveinheiten</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Aufnahme in den Bereich der Rehabilitation</t>
   </si>
   <si>
     <t>K</t>
   </si>
   <si>
-    <t>stationäre Aufnahme/ambulanter Besuch aus Kapazitätsgründen zugewiesen</t>
+    <t>Aufnahme eines 0-Tagesfalls</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Kennzeichen der Datensätze, die den Patientenaufenthalt nach dem Zeitpunkt der Asylierung beschreiben</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Aufnahme eines Frühgeborenen/Neugeborenen am Tag der Geburt oder am Folgetag in den allgemein stationären Bereich inkl. Aufnahme auf Intensiveinheiten</t>
+  </si>
+  <si>
+    <t>LKF_P</t>
+  </si>
+  <si>
+    <t>Aufnahme in den ausschließlichen Bereich der Pflege</t>
+  </si>
+  <si>
+    <t>KaOrg_3</t>
+  </si>
+  <si>
+    <t>Ambulanzfall</t>
+  </si>
+  <si>
+    <t>KaOrg_7</t>
+  </si>
+  <si>
+    <t>AUVA Wiederaufnahme (Diagnose der Aufnahme enthält Diagnose der Ersterkrankung. Aufnahmezahl AUFZL enthält jene des Erstberichtes).</t>
+  </si>
+  <si>
+    <t>KaOrg_8</t>
+  </si>
+  <si>
+    <t>Kurheilverfahren stationär</t>
+  </si>
+  <si>
+    <t>KaOrg_9</t>
+  </si>
+  <si>
+    <t>Rehabilitationsaufenthalt ambulant</t>
+  </si>
+  <si>
+    <t>KaOrg_U</t>
+  </si>
+  <si>
+    <t>Urgenz</t>
+  </si>
+  <si>
+    <t>KaOrg_1</t>
+  </si>
+  <si>
+    <t>Verlängerung</t>
+  </si>
+  <si>
+    <t>KaOrg_2</t>
+  </si>
+  <si>
+    <t>Asylierung</t>
+  </si>
+  <si>
+    <t>KaOrg_E</t>
+  </si>
+  <si>
+    <t>Erinnerung (Urgenz von Ambulanzmeldungen)</t>
+  </si>
+  <si>
+    <t>LKF_1</t>
+  </si>
+  <si>
+    <t>Fremdzuweisung von einem:einer Allgemeinmediziner:in</t>
+  </si>
+  <si>
+    <t>LKF_2</t>
+  </si>
+  <si>
+    <t>Fremdzuweisung von einem Facharzt/einer Fachärztin</t>
+  </si>
+  <si>
+    <t>LKF_3</t>
+  </si>
+  <si>
+    <t>Fremdzuweisung von der eigenen/einer anderen Krankenanstalt ohne bestehenden stationären Aufenthalt</t>
+  </si>
+  <si>
+    <t>LKF_4</t>
+  </si>
+  <si>
+    <t>Fremdzuweisung von einem Notarzt/einer Notärztin</t>
+  </si>
+  <si>
+    <t>LKF_5</t>
+  </si>
+  <si>
+    <t>Selbstzuweisung (ohne Einweisungsschein)</t>
+  </si>
+  <si>
+    <t>LKF_6</t>
+  </si>
+  <si>
+    <t>Wiederbestellung</t>
+  </si>
+  <si>
+    <t>LKF_9</t>
+  </si>
+  <si>
+    <t>Sonstige Zuweisung (durch Behörde, Pflegeeinrichtung, etc.)</t>
   </si>
   <si>
     <t>System URI</t>
@@ -382,7 +502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -423,18 +543,178 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
